--- a/data/use_cases/uc10_goz_2556_stricter_than_bep_result.xlsx
+++ b/data/use_cases/uc10_goz_2556_stricter_than_bep_result.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5">
@@ -5834,7 +5834,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дата построения 03.07.2026</t>
+          <t>Дата построения 10.07.2026</t>
         </is>
       </c>
     </row>
